--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/137.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/137.xlsx
@@ -426,13 +426,13 @@
         <v>3.811724568975099</v>
       </c>
       <c r="E2">
-        <v>-16.14269615246115</v>
+        <v>-19.80910127148389</v>
       </c>
       <c r="F2">
-        <v>-1.46044252797694</v>
+        <v>-3.176579560030703</v>
       </c>
       <c r="G2">
-        <v>-14.55657795468728</v>
+        <v>-15.34028170902603</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>4.145370884219259</v>
       </c>
       <c r="E3">
-        <v>-18.19938716657287</v>
+        <v>-21.28602475070617</v>
       </c>
       <c r="F3">
-        <v>-1.87013979152313</v>
+        <v>-2.860960810787855</v>
       </c>
       <c r="G3">
-        <v>-13.27937167715186</v>
+        <v>-15.22410488009378</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>4.426537772681094</v>
       </c>
       <c r="E4">
-        <v>-19.1626331627177</v>
+        <v>-22.66259833789794</v>
       </c>
       <c r="F4">
-        <v>-2.470566164461699</v>
+        <v>-3.024017478722313</v>
       </c>
       <c r="G4">
-        <v>-13.771913446339</v>
+        <v>-15.60085751592045</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>4.621016247293665</v>
       </c>
       <c r="E5">
-        <v>-19.24631621770167</v>
+        <v>-20.92447524524587</v>
       </c>
       <c r="F5">
-        <v>-1.96977747946666</v>
+        <v>-2.805562083990833</v>
       </c>
       <c r="G5">
-        <v>-13.40815318097</v>
+        <v>-15.09108222168738</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>4.74014451859225</v>
       </c>
       <c r="E6">
-        <v>-23.44958204541705</v>
+        <v>-23.02319675796485</v>
       </c>
       <c r="F6">
-        <v>-1.189393258474316</v>
+        <v>-3.062838088687109</v>
       </c>
       <c r="G6">
-        <v>-12.78357692020419</v>
+        <v>-16.38934676509471</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>4.788290137634323</v>
       </c>
       <c r="E7">
-        <v>-22.06121333806276</v>
+        <v>-24.12361917095744</v>
       </c>
       <c r="F7">
-        <v>-1.842430901899487</v>
+        <v>-2.768027928602585</v>
       </c>
       <c r="G7">
-        <v>-12.65166252287672</v>
+        <v>-16.29847196736724</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>4.781809427890993</v>
       </c>
       <c r="E8">
-        <v>-22.08531857659207</v>
+        <v>-25.00044514585525</v>
       </c>
       <c r="F8">
-        <v>-1.300047404507677</v>
+        <v>-2.305500705575453</v>
       </c>
       <c r="G8">
-        <v>-14.17861262799803</v>
+        <v>-16.12916779137814</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>4.735280566512142</v>
       </c>
       <c r="E9">
-        <v>-24.27473376501133</v>
+        <v>-26.55430271165865</v>
       </c>
       <c r="F9">
-        <v>-1.49989766737228</v>
+        <v>-2.476726732836319</v>
       </c>
       <c r="G9">
-        <v>-13.31956800624893</v>
+        <v>-15.79898561756774</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>4.66822691438291</v>
       </c>
       <c r="E10">
-        <v>-24.86726411830197</v>
+        <v>-26.09064235256611</v>
       </c>
       <c r="F10">
-        <v>-1.970337455830953</v>
+        <v>-2.204550055298485</v>
       </c>
       <c r="G10">
-        <v>-12.77402551111761</v>
+        <v>-16.30636294289388</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>4.598123184641419</v>
       </c>
       <c r="E11">
-        <v>-26.34782996385612</v>
+        <v>-27.64240254665048</v>
       </c>
       <c r="F11">
-        <v>-0.9223988474083964</v>
+        <v>-2.047201667136719</v>
       </c>
       <c r="G11">
-        <v>-11.95234978207341</v>
+        <v>-15.16698309381252</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>4.537858675860025</v>
       </c>
       <c r="E12">
-        <v>-26.25460698245902</v>
+        <v>-27.28571645165155</v>
       </c>
       <c r="F12">
-        <v>-0.7081548725527491</v>
+        <v>-1.971318242835868</v>
       </c>
       <c r="G12">
-        <v>-11.71074234000572</v>
+        <v>-15.7655354524941</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>4.494659686071412</v>
       </c>
       <c r="E13">
-        <v>-29.26806498304884</v>
+        <v>-29.00759633481222</v>
       </c>
       <c r="F13">
-        <v>-0.1874861982579255</v>
+        <v>-1.533246082274183</v>
       </c>
       <c r="G13">
-        <v>-12.20878103192944</v>
+        <v>-15.42447300060025</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>4.473753306550595</v>
       </c>
       <c r="E14">
-        <v>-26.14572224115599</v>
+        <v>-28.90629743399399</v>
       </c>
       <c r="F14">
-        <v>-0.6923446523029178</v>
+        <v>-1.716862829146124</v>
       </c>
       <c r="G14">
-        <v>-10.60041094061737</v>
+        <v>-15.18992762265152</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>4.472015306175059</v>
       </c>
       <c r="E15">
-        <v>-27.29369477060655</v>
+        <v>-31.21351846164201</v>
       </c>
       <c r="F15">
-        <v>-0.1824812024102108</v>
+        <v>-0.7938519654745664</v>
       </c>
       <c r="G15">
-        <v>-11.09456092847264</v>
+        <v>-14.70179148496188</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>4.481457203979128</v>
       </c>
       <c r="E16">
-        <v>-30.53988835081145</v>
+        <v>-31.88197367116184</v>
       </c>
       <c r="F16">
-        <v>-0.2790174827976596</v>
+        <v>-0.6337360018200471</v>
       </c>
       <c r="G16">
-        <v>-10.16633679654822</v>
+        <v>-13.98125861212201</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>4.493878854265814</v>
       </c>
       <c r="E17">
-        <v>-30.41722117772697</v>
+        <v>-33.5019399782282</v>
       </c>
       <c r="F17">
-        <v>0.4490644487493267</v>
+        <v>-0.6899763498983139</v>
       </c>
       <c r="G17">
-        <v>-8.245604168632401</v>
+        <v>-13.38616287927905</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>4.494332031099203</v>
       </c>
       <c r="E18">
-        <v>-31.89797184118508</v>
+        <v>-34.29657805421897</v>
       </c>
       <c r="F18">
-        <v>0.04477725271081952</v>
+        <v>-0.2314327457112448</v>
       </c>
       <c r="G18">
-        <v>-8.568973604432284</v>
+        <v>-12.56239594381737</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>4.466451127054412</v>
       </c>
       <c r="E19">
-        <v>-35.05484438203256</v>
+        <v>-35.56959131702614</v>
       </c>
       <c r="F19">
-        <v>0.5300390191077839</v>
+        <v>-0.2214451199356912</v>
       </c>
       <c r="G19">
-        <v>-8.42422609206719</v>
+        <v>-12.32384176754899</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>4.399179371864964</v>
       </c>
       <c r="E20">
-        <v>-37.45067832650712</v>
+        <v>-36.01199138734687</v>
       </c>
       <c r="F20">
-        <v>1.236095489781734</v>
+        <v>0.4039192536641564</v>
       </c>
       <c r="G20">
-        <v>-7.762813530493072</v>
+        <v>-10.82496238827132</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>4.280560471965515</v>
       </c>
       <c r="E21">
-        <v>-36.35750949709334</v>
+        <v>-37.80585057597815</v>
       </c>
       <c r="F21">
-        <v>0.8645114104383487</v>
+        <v>0.7988218753963479</v>
       </c>
       <c r="G21">
-        <v>-7.088872005626202</v>
+        <v>-11.27496207434627</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>4.102733540849682</v>
       </c>
       <c r="E22">
-        <v>-38.70041906965562</v>
+        <v>-38.55502344759602</v>
       </c>
       <c r="F22">
-        <v>2.284116106577168</v>
+        <v>0.9204444342101769</v>
       </c>
       <c r="G22">
-        <v>-7.124109225372458</v>
+        <v>-10.68465444708342</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>3.868224024878937</v>
       </c>
       <c r="E23">
-        <v>-38.78443230493991</v>
+        <v>-38.43582628257344</v>
       </c>
       <c r="F23">
-        <v>1.968037613425766</v>
+        <v>1.417565936713022</v>
       </c>
       <c r="G23">
-        <v>-6.609784708689368</v>
+        <v>-10.00322661210153</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>3.582429248022205</v>
       </c>
       <c r="E24">
-        <v>-38.50571859935332</v>
+        <v>-40.53037174130531</v>
       </c>
       <c r="F24">
-        <v>1.941678962668686</v>
+        <v>1.603941975403688</v>
       </c>
       <c r="G24">
-        <v>-5.754888560095549</v>
+        <v>-9.11860583096559</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>3.255253090928941</v>
       </c>
       <c r="E25">
-        <v>-38.65624343739908</v>
+        <v>-41.02971026228378</v>
       </c>
       <c r="F25">
-        <v>2.414575688844062</v>
+        <v>1.216907187263286</v>
       </c>
       <c r="G25">
-        <v>-6.453487262253189</v>
+        <v>-8.83937364322307</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>2.905332452837102</v>
       </c>
       <c r="E26">
-        <v>-38.50902247896222</v>
+        <v>-40.11330003024904</v>
       </c>
       <c r="F26">
-        <v>2.711605045200686</v>
+        <v>2.190737562729191</v>
       </c>
       <c r="G26">
-        <v>-4.518894191303151</v>
+        <v>-9.520155318918656</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>2.54955473410179</v>
       </c>
       <c r="E27">
-        <v>-41.59467782861719</v>
+        <v>-39.97911600216081</v>
       </c>
       <c r="F27">
-        <v>2.512276653799847</v>
+        <v>1.725645714222992</v>
       </c>
       <c r="G27">
-        <v>-6.945717047461687</v>
+        <v>-9.312665087167632</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>2.202832103070104</v>
       </c>
       <c r="E28">
-        <v>-41.58247569374485</v>
+        <v>-41.77591566441006</v>
       </c>
       <c r="F28">
-        <v>1.874007972799189</v>
+        <v>1.515565113933814</v>
       </c>
       <c r="G28">
-        <v>-6.473328921145649</v>
+        <v>-9.400495756701865</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>1.882481451116695</v>
       </c>
       <c r="E29">
-        <v>-39.60337289699791</v>
+        <v>-41.70531730170497</v>
       </c>
       <c r="F29">
-        <v>2.479085628704476</v>
+        <v>1.743488748079293</v>
       </c>
       <c r="G29">
-        <v>-5.500275693847225</v>
+        <v>-9.357291849835827</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>1.599760685166201</v>
       </c>
       <c r="E30">
-        <v>-41.68875014173022</v>
+        <v>-42.01683099372939</v>
       </c>
       <c r="F30">
-        <v>2.243219607900956</v>
+        <v>1.242926207385219</v>
       </c>
       <c r="G30">
-        <v>-6.185275027429756</v>
+        <v>-8.584191634653884</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>1.360765034169769</v>
       </c>
       <c r="E31">
-        <v>-43.07409531124003</v>
+        <v>-40.92214416557638</v>
       </c>
       <c r="F31">
-        <v>1.567899709707882</v>
+        <v>1.132054200724922</v>
       </c>
       <c r="G31">
-        <v>-5.628215232534732</v>
+        <v>-8.504041775706705</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>1.171787818258462</v>
       </c>
       <c r="E32">
-        <v>-40.32028777625584</v>
+        <v>-41.72551852158893</v>
       </c>
       <c r="F32">
-        <v>1.475922763505441</v>
+        <v>1.029001982347052</v>
       </c>
       <c r="G32">
-        <v>-5.672133178046439</v>
+        <v>-9.016815510102674</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>1.033452859783579</v>
       </c>
       <c r="E33">
-        <v>-38.20811816526707</v>
+        <v>-41.52275043828815</v>
       </c>
       <c r="F33">
-        <v>2.058220315833743</v>
+        <v>0.7998092893404849</v>
       </c>
       <c r="G33">
-        <v>-4.514735275169507</v>
+        <v>-8.448213613370338</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>0.9449994549531732</v>
       </c>
       <c r="E34">
-        <v>-39.96866444586188</v>
+        <v>-40.17765819293858</v>
       </c>
       <c r="F34">
-        <v>1.450707259764225</v>
+        <v>0.7694976693372454</v>
       </c>
       <c r="G34">
-        <v>-4.672959451113928</v>
+        <v>-8.839677794967933</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>0.9082890566997527</v>
       </c>
       <c r="E35">
-        <v>-38.72817082772812</v>
+        <v>-39.24172786767714</v>
       </c>
       <c r="F35">
-        <v>1.375300975087385</v>
+        <v>0.312682039552416</v>
       </c>
       <c r="G35">
-        <v>-4.967380950887546</v>
+        <v>-7.78623452021995</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>0.9217548780105647</v>
       </c>
       <c r="E36">
-        <v>-39.24424679034565</v>
+        <v>-39.52183912887454</v>
       </c>
       <c r="F36">
-        <v>0.9653104694806037</v>
+        <v>0.1596254229045542</v>
       </c>
       <c r="G36">
-        <v>-4.75705936662746</v>
+        <v>-8.503674966091655</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>0.9880402639491387</v>
       </c>
       <c r="E37">
-        <v>-37.7418350532229</v>
+        <v>-38.58004239261678</v>
       </c>
       <c r="F37">
-        <v>0.6147727207401453</v>
+        <v>-0.1581305142375166</v>
       </c>
       <c r="G37">
-        <v>-4.635633635694781</v>
+        <v>-8.48463611116096</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>1.111946059690301</v>
       </c>
       <c r="E38">
-        <v>-37.95520213182464</v>
+        <v>-38.30030284383296</v>
       </c>
       <c r="F38">
-        <v>1.15187868940872</v>
+        <v>-0.1551591603636747</v>
       </c>
       <c r="G38">
-        <v>-4.211982889405646</v>
+        <v>-7.252798047757614</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>1.293826669097002</v>
       </c>
       <c r="E39">
-        <v>-39.34317005428608</v>
+        <v>-38.14261579285753</v>
       </c>
       <c r="F39">
-        <v>0.5666934483142593</v>
+        <v>-0.3275821785215862</v>
       </c>
       <c r="G39">
-        <v>-4.661422570765798</v>
+        <v>-7.365968604293193</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>1.540812636008184</v>
       </c>
       <c r="E40">
-        <v>-36.28434860300082</v>
+        <v>-36.8157706814636</v>
       </c>
       <c r="F40">
-        <v>1.202725537327359</v>
+        <v>-0.640314067365678</v>
       </c>
       <c r="G40">
-        <v>-2.595851054424198</v>
+        <v>-7.175170168085452</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>1.858696383794285</v>
       </c>
       <c r="E41">
-        <v>-36.79720375023595</v>
+        <v>-38.41260567805632</v>
       </c>
       <c r="F41">
-        <v>0.3526076916325466</v>
+        <v>-0.4531179449462401</v>
       </c>
       <c r="G41">
-        <v>-2.432742175349804</v>
+        <v>-7.147394456380598</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>2.243893356415008</v>
       </c>
       <c r="E42">
-        <v>-34.67988831041571</v>
+        <v>-36.5637205925824</v>
       </c>
       <c r="F42">
-        <v>0.3735488195753181</v>
+        <v>-0.3513463825730985</v>
       </c>
       <c r="G42">
-        <v>-2.968563562996121</v>
+        <v>-7.004197726302625</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>2.701537875293735</v>
       </c>
       <c r="E43">
-        <v>-34.5571899882463</v>
+        <v>-36.51104126013828</v>
       </c>
       <c r="F43">
-        <v>0.3795395726323642</v>
+        <v>-0.7533945015218385</v>
       </c>
       <c r="G43">
-        <v>-2.425353768156953</v>
+        <v>-6.835217282642818</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>3.232010573591223</v>
       </c>
       <c r="E44">
-        <v>-35.14203690058601</v>
+        <v>-35.06837346792318</v>
       </c>
       <c r="F44">
-        <v>0.4877781993191616</v>
+        <v>-0.6172026168275718</v>
       </c>
       <c r="G44">
-        <v>-2.116455689625611</v>
+        <v>-6.383341776579157</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>3.823052076959257</v>
       </c>
       <c r="E45">
-        <v>-34.72670123186352</v>
+        <v>-34.82778208908719</v>
       </c>
       <c r="F45">
-        <v>1.02907819214811</v>
+        <v>-0.4615954569464903</v>
       </c>
       <c r="G45">
-        <v>-3.32998460121148</v>
+        <v>-6.372201729408876</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>4.472292344200475</v>
       </c>
       <c r="E46">
-        <v>-34.81779569245664</v>
+        <v>-34.36161526696012</v>
       </c>
       <c r="F46">
-        <v>1.666569864524942</v>
+        <v>-0.390966367081596</v>
       </c>
       <c r="G46">
-        <v>-2.850124523875676</v>
+        <v>-6.636505679579412</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>5.171655361652777</v>
       </c>
       <c r="E47">
-        <v>-34.1630543867314</v>
+        <v>-33.39464591686258</v>
       </c>
       <c r="F47">
-        <v>0.06069433235561202</v>
+        <v>-0.7625264237703002</v>
       </c>
       <c r="G47">
-        <v>-2.785874099488378</v>
+        <v>-6.262498241690296</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>5.899760866508069</v>
       </c>
       <c r="E48">
-        <v>-32.68615582677707</v>
+        <v>-33.49533014240474</v>
       </c>
       <c r="F48">
-        <v>0.5148401340012185</v>
+        <v>-0.44997843248963</v>
       </c>
       <c r="G48">
-        <v>-2.680441789920859</v>
+        <v>-6.645758158410318</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>6.64374369246091</v>
       </c>
       <c r="E49">
-        <v>-31.88005488752977</v>
+        <v>-32.22715121757967</v>
       </c>
       <c r="F49">
-        <v>0.7924898349693484</v>
+        <v>-0.7691169148269731</v>
       </c>
       <c r="G49">
-        <v>-2.879093345858669</v>
+        <v>-6.643108252650338</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>7.386236319030059</v>
       </c>
       <c r="E50">
-        <v>-29.73278025781788</v>
+        <v>-32.34810934420397</v>
       </c>
       <c r="F50">
-        <v>0.9167847070246087</v>
+        <v>-0.6025819321681605</v>
       </c>
       <c r="G50">
-        <v>-3.453065544214925</v>
+        <v>-7.42083601262003</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>8.099786004411108</v>
       </c>
       <c r="E51">
-        <v>-30.37816437842828</v>
+        <v>-30.78996566431335</v>
       </c>
       <c r="F51">
-        <v>0.8095359793841567</v>
+        <v>-0.6182331058766544</v>
       </c>
       <c r="G51">
-        <v>-3.933706234183472</v>
+        <v>-6.89265366364731</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>8.765712631423538</v>
       </c>
       <c r="E52">
-        <v>-29.38029928928534</v>
+        <v>-30.60550285992675</v>
       </c>
       <c r="F52">
-        <v>0.1684657598272305</v>
+        <v>-0.4138135684182092</v>
       </c>
       <c r="G52">
-        <v>-4.287697093292523</v>
+        <v>-7.394143759920488</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>9.36539968599444</v>
       </c>
       <c r="E53">
-        <v>-29.03856267845014</v>
+        <v>-31.17613955971855</v>
       </c>
       <c r="F53">
-        <v>-0.04646824507494882</v>
+        <v>-0.5585964514469096</v>
       </c>
       <c r="G53">
-        <v>-3.575686996170333</v>
+        <v>-6.932861741095046</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>9.875785582579429</v>
       </c>
       <c r="E54">
-        <v>-28.63904036184693</v>
+        <v>-28.34378649215921</v>
       </c>
       <c r="F54">
-        <v>-0.06031357784533976</v>
+        <v>-0.5397908546685551</v>
       </c>
       <c r="G54">
-        <v>-3.50356778758542</v>
+        <v>-7.386261921999917</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>10.28182146683418</v>
       </c>
       <c r="E55">
-        <v>-28.58069604915574</v>
+        <v>-27.96241163243984</v>
       </c>
       <c r="F55">
-        <v>-0.1138343957402158</v>
+        <v>-1.059742162792555</v>
       </c>
       <c r="G55">
-        <v>-4.890087246523046</v>
+        <v>-7.72941427493896</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>10.57157291543487</v>
       </c>
       <c r="E56">
-        <v>-24.92192037933671</v>
+        <v>-27.52097510714647</v>
       </c>
       <c r="F56">
-        <v>0.7773158008848672</v>
+        <v>-0.6380633931322718</v>
       </c>
       <c r="G56">
-        <v>-3.436362000320982</v>
+        <v>-7.936157833736925</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>10.73422733193139</v>
       </c>
       <c r="E57">
-        <v>-25.24952568863919</v>
+        <v>-26.30661764787985</v>
       </c>
       <c r="F57">
-        <v>0.06970282786105665</v>
+        <v>-1.236123120401042</v>
       </c>
       <c r="G57">
-        <v>-4.022724792506661</v>
+        <v>-8.074920214126893</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>10.76528742162723</v>
       </c>
       <c r="E58">
-        <v>-24.85446807421017</v>
+        <v>-26.52017992741386</v>
       </c>
       <c r="F58">
-        <v>-0.1826187113990756</v>
+        <v>-1.257949773097406</v>
       </c>
       <c r="G58">
-        <v>-5.587393630108084</v>
+        <v>-8.675805273100639</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>10.66622844489137</v>
       </c>
       <c r="E59">
-        <v>-24.14217571915678</v>
+        <v>-26.56209413610403</v>
       </c>
       <c r="F59">
-        <v>0.5528000702345059</v>
+        <v>-0.9459294518523192</v>
       </c>
       <c r="G59">
-        <v>-4.987533288386349</v>
+        <v>-8.889567818731813</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>10.44617105148017</v>
       </c>
       <c r="E60">
-        <v>-23.71829066492213</v>
+        <v>-25.80819906320982</v>
       </c>
       <c r="F60">
-        <v>-0.5289491821007153</v>
+        <v>-0.7856287622669756</v>
       </c>
       <c r="G60">
-        <v>-3.988965254198976</v>
+        <v>-9.208078658847635</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>10.11716726106496</v>
       </c>
       <c r="E61">
-        <v>-22.91421233959002</v>
+        <v>-24.17116928741541</v>
       </c>
       <c r="F61">
-        <v>-0.3446092704861301</v>
+        <v>-1.852056531120017</v>
       </c>
       <c r="G61">
-        <v>-6.320553369162882</v>
+        <v>-9.156284096904537</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>9.69455173331621</v>
       </c>
       <c r="E62">
-        <v>-21.95132351961912</v>
+        <v>-23.73979599316209</v>
       </c>
       <c r="F62">
-        <v>-0.6284874659559094</v>
+        <v>-1.215298792262065</v>
       </c>
       <c r="G62">
-        <v>-5.083188359460149</v>
+        <v>-10.20348508133517</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>9.204154202112488</v>
       </c>
       <c r="E63">
-        <v>-22.18479629424436</v>
+        <v>-23.05729877615302</v>
       </c>
       <c r="F63">
-        <v>-0.6700450018195551</v>
+        <v>-1.785807019713724</v>
       </c>
       <c r="G63">
-        <v>-5.984252915403215</v>
+        <v>-10.57198384813704</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>8.668139477907003</v>
       </c>
       <c r="E64">
-        <v>-20.1877661608138</v>
+        <v>-22.8783950451247</v>
       </c>
       <c r="F64">
-        <v>-0.4544872362630677</v>
+        <v>-1.853707467353797</v>
       </c>
       <c r="G64">
-        <v>-6.389505744558775</v>
+        <v>-10.1236563439727</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>8.108565069338583</v>
       </c>
       <c r="E65">
-        <v>-19.59217073756544</v>
+        <v>-22.35035991049732</v>
       </c>
       <c r="F65">
-        <v>-0.5225210510549911</v>
+        <v>-2.088673881157876</v>
       </c>
       <c r="G65">
-        <v>-7.48377845396718</v>
+        <v>-10.05451860571084</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>7.557365408295076</v>
       </c>
       <c r="E66">
-        <v>-20.87964548220567</v>
+        <v>-22.04345420643779</v>
       </c>
       <c r="F66">
-        <v>-1.715974819290323</v>
+        <v>-1.867059921519522</v>
       </c>
       <c r="G66">
-        <v>-7.169591006894243</v>
+        <v>-10.72087461216823</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>7.036136605256543</v>
       </c>
       <c r="E67">
-        <v>-20.49960172671591</v>
+        <v>-21.10411824789</v>
       </c>
       <c r="F67">
-        <v>-1.075105064644874</v>
+        <v>-2.42030248719463</v>
       </c>
       <c r="G67">
-        <v>-6.647228007615114</v>
+        <v>-10.60634646844527</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>6.562938180363379</v>
       </c>
       <c r="E68">
-        <v>-19.17794189966102</v>
+        <v>-21.56414870028463</v>
       </c>
       <c r="F68">
-        <v>-1.836360625571772</v>
+        <v>-2.343777078156609</v>
       </c>
       <c r="G68">
-        <v>-8.226796364598021</v>
+        <v>-11.61179381463023</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>6.162796955247951</v>
       </c>
       <c r="E69">
-        <v>-19.38514561265671</v>
+        <v>-20.92073735505352</v>
       </c>
       <c r="F69">
-        <v>-1.389485404620537</v>
+        <v>-3.007467526381782</v>
       </c>
       <c r="G69">
-        <v>-5.90584442309831</v>
+        <v>-11.3035680028311</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>5.84699188585175</v>
       </c>
       <c r="E70">
-        <v>-19.83338509810016</v>
+        <v>-21.01564238703718</v>
       </c>
       <c r="F70">
-        <v>-1.496699340830071</v>
+        <v>-2.661019427508944</v>
       </c>
       <c r="G70">
-        <v>-7.381001271648823</v>
+        <v>-11.00306868964937</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>5.623458792107627</v>
       </c>
       <c r="E71">
-        <v>-17.79080669607021</v>
+        <v>-20.52668481776511</v>
       </c>
       <c r="F71">
-        <v>-1.49772568804214</v>
+        <v>-2.893978707096041</v>
       </c>
       <c r="G71">
-        <v>-7.300271827402418</v>
+        <v>-11.08001908110013</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>5.504389351473796</v>
       </c>
       <c r="E72">
-        <v>-19.57656712261806</v>
+        <v>-21.76477787975313</v>
       </c>
       <c r="F72">
-        <v>-2.681639977266832</v>
+        <v>-3.003326517735187</v>
       </c>
       <c r="G72">
-        <v>-7.069959771808177</v>
+        <v>-10.47597502117114</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>5.48798602682202</v>
       </c>
       <c r="E73">
-        <v>-18.87198728099487</v>
+        <v>-20.53693079010347</v>
       </c>
       <c r="F73">
-        <v>-2.436614698090558</v>
+        <v>-3.241400137667168</v>
       </c>
       <c r="G73">
-        <v>-6.019732934396445</v>
+        <v>-10.7178853096114</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>5.571973077476491</v>
       </c>
       <c r="E74">
-        <v>-19.83421574036512</v>
+        <v>-21.65198911980476</v>
       </c>
       <c r="F74">
-        <v>-2.940930571486717</v>
+        <v>-3.248794973471959</v>
       </c>
       <c r="G74">
-        <v>-6.798087273068004</v>
+        <v>-10.08153720148427</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>5.755659104317968</v>
       </c>
       <c r="E75">
-        <v>-21.64549765050405</v>
+        <v>-21.04810803996336</v>
       </c>
       <c r="F75">
-        <v>-1.967554969724949</v>
+        <v>-3.174780346031823</v>
       </c>
       <c r="G75">
-        <v>-5.56993297028272</v>
+        <v>-10.38406506321329</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>6.025515088615421</v>
       </c>
       <c r="E76">
-        <v>-18.36099277243327</v>
+        <v>-21.07013251961893</v>
       </c>
       <c r="F76">
-        <v>-2.225049663415565</v>
+        <v>-3.924205163711938</v>
       </c>
       <c r="G76">
-        <v>-6.115455884829614</v>
+        <v>-9.332450615051384</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>6.371476607508661</v>
       </c>
       <c r="E77">
-        <v>-19.96563165310535</v>
+        <v>-22.01164060768961</v>
       </c>
       <c r="F77">
-        <v>-2.48371318351153</v>
+        <v>-3.788265102708123</v>
       </c>
       <c r="G77">
-        <v>-6.487460881617346</v>
+        <v>-9.021606226427368</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>6.783751564770013</v>
       </c>
       <c r="E78">
-        <v>-19.82576810853042</v>
+        <v>-22.10551149005338</v>
       </c>
       <c r="F78">
-        <v>-2.454340932143065</v>
+        <v>-3.714405379972311</v>
       </c>
       <c r="G78">
-        <v>-5.693481236567973</v>
+        <v>-9.240749516660825</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>7.241467457506338</v>
       </c>
       <c r="E79">
-        <v>-20.98764143628518</v>
+        <v>-21.94663039082207</v>
       </c>
       <c r="F79">
-        <v>-3.098773494987954</v>
+        <v>-3.410102957819106</v>
       </c>
       <c r="G79">
-        <v>-4.984985201665423</v>
+        <v>-9.14909149555602</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>7.731437967746217</v>
       </c>
       <c r="E80">
-        <v>-20.59036185379738</v>
+        <v>-23.14517657457506</v>
       </c>
       <c r="F80">
-        <v>-1.696368191233461</v>
+        <v>-4.155335408073654</v>
       </c>
       <c r="G80">
-        <v>-4.980552157349713</v>
+        <v>-8.515455951059053</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>8.240798532439175</v>
       </c>
       <c r="E81">
-        <v>-23.95669330138994</v>
+        <v>-23.08697762428024</v>
       </c>
       <c r="F81">
-        <v>-2.223498959637524</v>
+        <v>-4.008871767584673</v>
       </c>
       <c r="G81">
-        <v>-2.996589906181722</v>
+        <v>-8.039202617375871</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>8.748615336055403</v>
       </c>
       <c r="E82">
-        <v>-23.02755347664459</v>
+        <v>-23.60621625732163</v>
       </c>
       <c r="F82">
-        <v>-3.031618578010401</v>
+        <v>-3.797908127644112</v>
       </c>
       <c r="G82">
-        <v>-3.821663519311254</v>
+        <v>-8.224588980046235</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>9.245712000674962</v>
       </c>
       <c r="E83">
-        <v>-23.09295409537667</v>
+        <v>-25.53753012795942</v>
       </c>
       <c r="F83">
-        <v>-2.409414426052234</v>
+        <v>-3.951231478595675</v>
       </c>
       <c r="G83">
-        <v>-2.718540385738975</v>
+        <v>-7.451948255912327</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>9.723137965084831</v>
       </c>
       <c r="E84">
-        <v>-24.29912142191072</v>
+        <v>-25.91007318379654</v>
       </c>
       <c r="F84">
-        <v>-3.336528193469857</v>
+        <v>-4.074511600582506</v>
       </c>
       <c r="G84">
-        <v>-2.994764995712534</v>
+        <v>-7.296635060186998</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>10.16390068285146</v>
       </c>
       <c r="E85">
-        <v>-27.38683468777715</v>
+        <v>-27.25917327807457</v>
       </c>
       <c r="F85">
-        <v>-2.761128456504668</v>
+        <v>-4.038982094309032</v>
       </c>
       <c r="G85">
-        <v>-2.967592366008227</v>
+        <v>-7.733440043098457</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>10.56163491469792</v>
       </c>
       <c r="E86">
-        <v>-27.10021742103941</v>
+        <v>-27.99443704496559</v>
       </c>
       <c r="F86">
-        <v>-1.932811584116733</v>
+        <v>-4.2434968940188</v>
       </c>
       <c r="G86">
-        <v>-2.501336878736714</v>
+        <v>-6.81958153328664</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>10.9093411046456</v>
       </c>
       <c r="E87">
-        <v>-27.52219199806464</v>
+        <v>-30.12749730891826</v>
       </c>
       <c r="F87">
-        <v>-3.34408041908118</v>
+        <v>-3.953738946723949</v>
       </c>
       <c r="G87">
-        <v>-3.195304119989719</v>
+        <v>-6.956582966449901</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>11.19208341459106</v>
       </c>
       <c r="E88">
-        <v>-28.77809403021352</v>
+        <v>-30.62399088013922</v>
       </c>
       <c r="F88">
-        <v>-3.24791359055538</v>
+        <v>-4.25537733930975</v>
       </c>
       <c r="G88">
-        <v>-2.800760565146906</v>
+        <v>-7.334433420377136</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>11.40352739767626</v>
       </c>
       <c r="E89">
-        <v>-29.87106765869503</v>
+        <v>-32.19853766815726</v>
       </c>
       <c r="F89">
-        <v>-3.388557950039694</v>
+        <v>-3.790335192847719</v>
       </c>
       <c r="G89">
-        <v>-3.59504827805803</v>
+        <v>-6.756425010883018</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>11.53760481384132</v>
       </c>
       <c r="E90">
-        <v>-34.2965157560491</v>
+        <v>-34.35399412417906</v>
       </c>
       <c r="F90">
-        <v>-2.814665841747599</v>
+        <v>-4.243627776068442</v>
       </c>
       <c r="G90">
-        <v>-3.191077324496707</v>
+        <v>-6.915145228299751</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>11.5826963223231</v>
       </c>
       <c r="E91">
-        <v>-34.80307463491579</v>
+        <v>-34.99874072685111</v>
       </c>
       <c r="F91">
-        <v>-3.196675753222619</v>
+        <v>-4.072333822680546</v>
       </c>
       <c r="G91">
-        <v>-3.717223292688358</v>
+        <v>-7.6866868289608</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>11.53152443378107</v>
       </c>
       <c r="E92">
-        <v>-34.31970521148128</v>
+        <v>-36.60391329517843</v>
       </c>
       <c r="F92">
-        <v>-2.986205820254127</v>
+        <v>-4.297487396231063</v>
       </c>
       <c r="G92">
-        <v>-3.935546809120207</v>
+        <v>-7.66940369976763</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>11.37791884351011</v>
       </c>
       <c r="E93">
-        <v>-36.35255471598282</v>
+        <v>-38.89888234941821</v>
       </c>
       <c r="F93">
-        <v>-2.452863124696471</v>
+        <v>-3.790893512477206</v>
       </c>
       <c r="G93">
-        <v>-4.486745482408182</v>
+        <v>-7.882799435783753</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>11.11362980622373</v>
       </c>
       <c r="E94">
-        <v>-39.40897353451666</v>
+        <v>-39.00214987240441</v>
       </c>
       <c r="F94">
-        <v>-2.578854493192664</v>
+        <v>-3.598554056853786</v>
       </c>
       <c r="G94">
-        <v>-4.135516791076529</v>
+        <v>-8.145059172939446</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>10.73643021239155</v>
       </c>
       <c r="E95">
-        <v>-41.33205158709733</v>
+        <v>-43.35140938461016</v>
       </c>
       <c r="F95">
-        <v>-3.054459152407792</v>
+        <v>-3.560470693877481</v>
       </c>
       <c r="G95">
-        <v>-5.881778579457428</v>
+        <v>-8.305031242387617</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>10.23808873892312</v>
       </c>
       <c r="E96">
-        <v>-44.95645735659773</v>
+        <v>-44.62707862605956</v>
       </c>
       <c r="F96">
-        <v>-1.583462542599291</v>
+        <v>-3.411681826088842</v>
       </c>
       <c r="G96">
-        <v>-4.402943191778036</v>
+        <v>-7.937233460508464</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>9.63316540942871</v>
       </c>
       <c r="E97">
-        <v>-46.3173401114043</v>
+        <v>-46.40859550893627</v>
       </c>
       <c r="F97">
-        <v>-2.164425595041683</v>
+        <v>-3.036760254479578</v>
       </c>
       <c r="G97">
-        <v>-5.319909793025573</v>
+        <v>-9.459839286630165</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>8.9025781687233</v>
       </c>
       <c r="E98">
-        <v>-47.91038737926878</v>
+        <v>-47.66333775682268</v>
       </c>
       <c r="F98">
-        <v>-1.561813988894529</v>
+        <v>-3.178199846670579</v>
       </c>
       <c r="G98">
-        <v>-6.590650561581098</v>
+        <v>-9.22409688228641</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>8.090603925899643</v>
       </c>
       <c r="E99">
-        <v>-50.2577066239552</v>
+        <v>-51.31536964975302</v>
       </c>
       <c r="F99">
-        <v>-1.12944845137073</v>
+        <v>-2.810924106189154</v>
       </c>
       <c r="G99">
-        <v>-7.357353147142519</v>
+        <v>-10.01734551885027</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>7.156173131052441</v>
       </c>
       <c r="E100">
-        <v>-51.0444504835203</v>
+        <v>-52.73906972584762</v>
       </c>
       <c r="F100">
-        <v>-0.9738926502686222</v>
+        <v>-2.277015635695386</v>
       </c>
       <c r="G100">
-        <v>-6.564360363548587</v>
+        <v>-11.28950653246336</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>6.200109986504627</v>
       </c>
       <c r="E101">
-        <v>-53.2533473479615</v>
+        <v>-56.02828019234943</v>
       </c>
       <c r="F101">
-        <v>-0.20269668050813</v>
+        <v>-2.199131704116774</v>
       </c>
       <c r="G101">
-        <v>-7.664413261481717</v>
+        <v>-10.94567016444145</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>5.091983789194708</v>
       </c>
       <c r="E102">
-        <v>-56.53021395125451</v>
+        <v>-57.1988108891108</v>
       </c>
       <c r="F102">
-        <v>-0.3879643636138506</v>
+        <v>-1.700871196435079</v>
       </c>
       <c r="G102">
-        <v>-8.331416732597704</v>
+        <v>-10.96172885442138</v>
       </c>
     </row>
   </sheetData>
